--- a/_pruebas_JAL-E02_Auth_Sesion.xlsx
+++ b/_pruebas_JAL-E02_Auth_Sesion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JUAN ECHAVARRIA\Desktop\Voz local\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9232705C-3F12-4A1E-9863-876C820BC249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E592B355-8CBD-41BD-AA41-CB0BCE62D19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Casos" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="550">
   <si>
     <t>Casos de prueba</t>
   </si>
@@ -1129,9 +1129,6 @@
     <t>Local Dev / Chromium (Playwright 1.63) - Windows 11</t>
   </si>
   <si>
-    <t>Juan José Echavarria Castaño</t>
-  </si>
-  <si>
     <t>Aprobado</t>
   </si>
   <si>
@@ -1297,9 +1294,6 @@
     <t>Reinicio continuo de inactividad ante interacción del usuario.</t>
   </si>
   <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
     <t>Tras el cierre por inactividad, cualquier intento de interactuar o navegar en páginas privadas es bloqueado y pide nuevo login.</t>
   </si>
   <si>
@@ -1309,9 +1303,6 @@
     <t>Zonas protegidas bloqueadas tras expiración automática.</t>
   </si>
   <si>
-    <t>14/10/2026</t>
-  </si>
-  <si>
     <t>La pantalla de perfil muestra de forma ordenada el nombre completo, número de cédula, ciudad de expedición, correo y rol asignado.</t>
   </si>
   <si>
@@ -1330,9 +1321,6 @@
     <t>Lectura fresca de datos desde Firestore sin información desfasada.</t>
   </si>
   <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
     <t>La vista de perfil está aislada para el usuario conectado; no es posible ver ni alterar la información de otra cuenta.</t>
   </si>
   <si>
@@ -1351,9 +1339,6 @@
     <t>Diseño responsivo del perfil validado.</t>
   </si>
   <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
     <t>Al ingresar la clave actual correcta y la nueva confirmada, el sistema la actualiza con éxito y avisa con notificación verde.</t>
   </si>
   <si>
@@ -1486,27 +1471,18 @@
     <t>21/10/2026</t>
   </si>
   <si>
-    <t>Al probar con correos no registrados, el mensaje en pantalla es el mismo, protegiendo la privacidad de los usuarios registrados.</t>
-  </si>
-  <si>
     <t>EVID-037</t>
   </si>
   <si>
     <t>Mensaje genérico de privacidad implementado.</t>
   </si>
   <si>
-    <t>Si se envía el campo en blanco o sin arroba y dominio, el formulario lo detiene de inmediato y solicita corregirlo.</t>
-  </si>
-  <si>
     <t>EVID-038</t>
   </si>
   <si>
     <t>Validación de formato de correo activa antes de enviar.</t>
   </si>
   <si>
-    <t>Los enlaces vencidos o usados no permiten cambiar clave; la app muestra aviso claro y ofrece botón para volver al login.</t>
-  </si>
-  <si>
     <t>EVID-039</t>
   </si>
   <si>
@@ -1768,21 +1744,12 @@
     <t>CP-018-01_Solicitud_Recuperacion.gif</t>
   </si>
   <si>
-    <t>Mensaje genérico seguro que no revela existencia de cuentas.</t>
-  </si>
-  <si>
     <t>CP-018-02_Respuesta_Generica_Privacidad.gif</t>
   </si>
   <si>
-    <t>Detección de correo inválido o vacío en recuperación de clave.</t>
-  </si>
-  <si>
     <t>CP-018-03_Validacion_Correo_Recuperacion.gif</t>
   </si>
   <si>
-    <t>Manejo de enlace inválido con enlace seguro de vuelta al login.</t>
-  </si>
-  <si>
     <t>CP-018-04_Retorno_Login.gif</t>
   </si>
   <si>
@@ -1808,6 +1775,30 @@
   </si>
   <si>
     <t>CP-019-04_Responsive_Y_Teclado.gif</t>
+  </si>
+  <si>
+    <t>Juan José Echavarría Castaño</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Rodríguez Gutiérrez</t>
+  </si>
+  <si>
+    <t>Se muestra mensaje informativo: 'Si el correo está registrado, te enviamos un enlace para restablecer tu contraseña', protegiendo la privacidad de los usuarios.</t>
+  </si>
+  <si>
+    <t>Se confirma la recepción del correo oficial emitido por Firebase Auth (noreply@jal3-fd8a2.firebaseapp.com) con el enlace seguro de restablecimiento.</t>
+  </si>
+  <si>
+    <t>El enlace recibido direcciona correctamente a la interfaz de restablecimiento de contraseña de Firebase, permitiendo ingresar y guardar la nueva clave.</t>
+  </si>
+  <si>
+    <t>Mensaje informativo genérico de restablecimiento de contraseña sin revelar existencia de cuentas.</t>
+  </si>
+  <si>
+    <t>Recepción de correo oficial de Firebase Auth con enlace para restablecer contraseña.</t>
+  </si>
+  <si>
+    <t>Interfaz oficial de Firebase Auth para restablecimiento seguro de la nueva clave.</t>
   </si>
 </sst>
 </file>
@@ -1979,9 +1970,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1999,6 +1987,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3847,156 +3838,6 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>420053</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3132773</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>1733550</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Imagen 74">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{374EE6D5-9207-0F31-5C3D-08A7CE108BDA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11411903" y="65455800"/>
-          <a:ext cx="2712720" cy="1695450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>420053</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3132773</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>1733550</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Imagen 76">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96D2A872-EB8B-02F6-0769-1FFA00789BF0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11411903" y="67227450"/>
-          <a:ext cx="2712720" cy="1695450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>420053</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3132773</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>1733550</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Imagen 78">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A595F31-422D-FDC0-6921-BAD8B3CA0E03}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11411903" y="68999100"/>
-          <a:ext cx="2712720" cy="1695450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>420053</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
@@ -4020,7 +3861,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4070,7 +3911,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4120,7 +3961,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4170,7 +4011,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4185,6 +4026,156 @@
         <a:xfrm>
           <a:off x="12344400" y="76085700"/>
           <a:ext cx="847725" cy="1695450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>176481</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3376344</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>1733550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80747E50-016A-D388-12BE-AF480D99D7AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11168331" y="65455800"/>
+          <a:ext cx="3199863" cy="1695450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>344425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3514725</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>1427225</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95DFD89B-340D-AA52-E33C-7BD00F58C1E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11029950" y="67533775"/>
+          <a:ext cx="3476625" cy="1082800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>160530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3514725</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>1611122</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagen 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1050B0A7-654F-090E-ABFB-6C9BFCD8E0B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11029950" y="69121530"/>
+          <a:ext cx="3476625" cy="1450592"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6082,1377 +6073,1377 @@
       <c r="A7" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="B7" s="18">
-        <v>46032</v>
+      <c r="B7" s="24" t="s">
+        <v>402</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="G7" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="H7" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18" t="s">
         <v>329</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="L7" s="21"/>
+      <c r="L7" s="20"/>
     </row>
     <row r="8" spans="1:12" ht="45" customHeight="1">
       <c r="A8" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="18">
-        <v>46032</v>
+      <c r="B8" s="24" t="s">
+        <v>402</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="H8" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="L8" s="21"/>
+      <c r="L8" s="20"/>
     </row>
     <row r="9" spans="1:12" ht="45" customHeight="1">
       <c r="A9" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="B9" s="18">
-        <v>46063</v>
+      <c r="B9" s="24" t="s">
+        <v>402</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F9" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="H9" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="L9" s="21"/>
+      <c r="L9" s="20"/>
     </row>
     <row r="10" spans="1:12" ht="45" customHeight="1">
       <c r="A10" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="B10" s="18">
-        <v>46063</v>
+      <c r="B10" s="24" t="s">
+        <v>402</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="H10" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="L10" s="21"/>
+      <c r="L10" s="20"/>
     </row>
     <row r="11" spans="1:12" ht="45" customHeight="1">
       <c r="A11" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="B11" s="18">
-        <v>46091</v>
+      <c r="B11" s="24" t="s">
+        <v>409</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" s="19" t="s">
         <v>340</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19" t="s">
-        <v>342</v>
-      </c>
-      <c r="L11" s="21"/>
+      <c r="L11" s="20"/>
     </row>
     <row r="12" spans="1:12" ht="45" customHeight="1">
       <c r="A12" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="B12" s="18">
-        <v>46122</v>
+      <c r="B12" s="24" t="s">
+        <v>409</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F12" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="H12" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="L12" s="21"/>
+      <c r="L12" s="20"/>
     </row>
     <row r="13" spans="1:12" ht="45" customHeight="1">
       <c r="A13" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="B13" s="18">
-        <v>46152</v>
+      <c r="B13" s="24" t="s">
+        <v>409</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="H13" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="L13" s="21"/>
+      <c r="L13" s="20"/>
     </row>
     <row r="14" spans="1:12" ht="45" customHeight="1">
       <c r="A14" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="B14" s="18">
-        <v>46152</v>
+      <c r="B14" s="24" t="s">
+        <v>409</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F14" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F14" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="H14" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="L14" s="21"/>
+      <c r="L14" s="20"/>
     </row>
     <row r="15" spans="1:12" ht="45" customHeight="1">
       <c r="A15" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="B15" s="18">
-        <v>46183</v>
+      <c r="B15" s="24" t="s">
+        <v>409</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="H15" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="L15" s="21"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12" ht="45" customHeight="1">
       <c r="A16" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="B16" s="18">
-        <v>46213</v>
+      <c r="B16" s="24" t="s">
+        <v>409</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F16" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F16" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="H16" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="L16" s="21"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" spans="1:12" ht="45" customHeight="1">
       <c r="A17" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="B17" s="18">
-        <v>46244</v>
+      <c r="B17" s="24" t="s">
+        <v>409</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F17" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F17" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="H17" s="19" t="s">
         <v>358</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18" t="s">
         <v>359</v>
       </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="L17" s="21"/>
+      <c r="L17" s="20"/>
     </row>
     <row r="18" spans="1:12" ht="45" customHeight="1">
       <c r="A18" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="B18" s="18">
-        <v>46244</v>
+      <c r="B18" s="24" t="s">
+        <v>409</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F18" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="H18" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="L18" s="21"/>
+      <c r="L18" s="20"/>
     </row>
     <row r="19" spans="1:12" ht="45" customHeight="1">
       <c r="A19" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B19" s="18">
-        <v>46275</v>
+      <c r="B19" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F19" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="H19" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="L19" s="21"/>
+      <c r="L19" s="20"/>
     </row>
     <row r="20" spans="1:12" ht="45" customHeight="1">
       <c r="A20" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="B20" s="18">
-        <v>46275</v>
+      <c r="B20" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F20" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="H20" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="L20" s="21"/>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" spans="1:12" ht="45" customHeight="1">
       <c r="A21" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="B21" s="18">
-        <v>46305</v>
+      <c r="B21" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F21" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="H21" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="H21" s="20" t="s">
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="L21" s="21"/>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="1:12" ht="45" customHeight="1">
       <c r="A22" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="B22" s="18">
-        <v>46336</v>
+      <c r="B22" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F22" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="H22" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="L22" s="21"/>
+      <c r="L22" s="20"/>
     </row>
     <row r="23" spans="1:12" ht="45" customHeight="1">
       <c r="A23" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="B23" s="18">
-        <v>46366</v>
+      <c r="B23" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F23" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="H23" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18" t="s">
         <v>377</v>
       </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="L23" s="21"/>
+      <c r="L23" s="20"/>
     </row>
     <row r="24" spans="1:12" ht="45" customHeight="1">
       <c r="A24" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="B24" s="18">
-        <v>46366</v>
+      <c r="B24" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F24" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F24" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="H24" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19" t="s">
-        <v>381</v>
-      </c>
-      <c r="L24" s="21"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" ht="45" customHeight="1">
       <c r="A25" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>382</v>
+      <c r="B25" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F25" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F25" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="H25" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19" t="s">
-        <v>385</v>
-      </c>
-      <c r="L25" s="21"/>
+      <c r="L25" s="20"/>
     </row>
     <row r="26" spans="1:12" ht="45" customHeight="1">
       <c r="A26" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>386</v>
+      <c r="B26" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F26" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F26" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19" t="s">
-        <v>389</v>
-      </c>
-      <c r="L26" s="21"/>
+      <c r="G26" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="L26" s="20"/>
     </row>
     <row r="27" spans="1:12" ht="45" customHeight="1">
       <c r="A27" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>386</v>
+      <c r="B27" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F27" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F27" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="L27" s="21"/>
+      <c r="G27" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="L27" s="20"/>
     </row>
     <row r="28" spans="1:12" ht="45" customHeight="1">
       <c r="A28" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>393</v>
+      <c r="B28" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F28" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>394</v>
-      </c>
-      <c r="H28" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="L28" s="21"/>
+      <c r="G28" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="L28" s="20"/>
     </row>
     <row r="29" spans="1:12" ht="45" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>393</v>
+      <c r="B29" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F29" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F29" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="L29" s="21"/>
+      <c r="G29" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="L29" s="20"/>
     </row>
     <row r="30" spans="1:12" ht="45" customHeight="1">
       <c r="A30" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>400</v>
+      <c r="B30" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="H30" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="L30" s="21"/>
+      <c r="G30" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="L30" s="20"/>
     </row>
     <row r="31" spans="1:12" ht="45" customHeight="1">
       <c r="A31" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>400</v>
+      <c r="B31" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F31" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F31" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>404</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>405</v>
-      </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19" t="s">
-        <v>406</v>
-      </c>
-      <c r="L31" s="21"/>
+      <c r="G31" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="L31" s="20"/>
     </row>
     <row r="32" spans="1:12" ht="45" customHeight="1">
       <c r="A32" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>407</v>
+      <c r="B32" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>408</v>
-      </c>
-      <c r="H32" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="L32" s="21"/>
+      <c r="G32" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="L32" s="20"/>
     </row>
     <row r="33" spans="1:12" ht="45" customHeight="1">
       <c r="A33" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>407</v>
+      <c r="B33" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F33" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="H33" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="L33" s="21"/>
+      <c r="G33" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="L33" s="20"/>
     </row>
     <row r="34" spans="1:12" ht="45" customHeight="1">
       <c r="A34" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>414</v>
+      <c r="B34" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F34" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>416</v>
-      </c>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="L34" s="21"/>
+      <c r="G34" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="L34" s="20"/>
     </row>
     <row r="35" spans="1:12" ht="45" customHeight="1">
       <c r="A35" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>414</v>
+      <c r="B35" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F35" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F35" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="L35" s="21"/>
+      <c r="G35" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="L35" s="20"/>
     </row>
     <row r="36" spans="1:12" ht="45" customHeight="1">
       <c r="A36" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>421</v>
+      <c r="B36" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F36" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F36" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19" t="s">
-        <v>424</v>
-      </c>
-      <c r="L36" s="21"/>
+      <c r="G36" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="L36" s="20"/>
     </row>
     <row r="37" spans="1:12" ht="45" customHeight="1">
       <c r="A37" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>421</v>
+      <c r="B37" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F37" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F37" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>425</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19" t="s">
-        <v>427</v>
-      </c>
-      <c r="L37" s="21"/>
+      <c r="G37" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="L37" s="20"/>
     </row>
     <row r="38" spans="1:12" ht="45" customHeight="1">
       <c r="A38" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>421</v>
+      <c r="B38" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F38" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F38" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="H38" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19" t="s">
-        <v>430</v>
-      </c>
-      <c r="L38" s="21"/>
+      <c r="G38" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="L38" s="20"/>
     </row>
     <row r="39" spans="1:12" ht="45" customHeight="1">
       <c r="A39" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>431</v>
+      <c r="B39" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F39" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>432</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>433</v>
-      </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="L39" s="21"/>
+      <c r="G39" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="L39" s="20"/>
     </row>
     <row r="40" spans="1:12" ht="45" customHeight="1">
       <c r="A40" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>431</v>
+      <c r="B40" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F40" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F40" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="H40" s="20" t="s">
-        <v>436</v>
-      </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="L40" s="21"/>
+      <c r="G40" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="L40" s="20"/>
     </row>
     <row r="41" spans="1:12" ht="45" customHeight="1">
       <c r="A41" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>431</v>
+      <c r="B41" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F41" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F41" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="L41" s="21"/>
+      <c r="G41" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="L41" s="20"/>
     </row>
     <row r="42" spans="1:12" ht="45" customHeight="1">
       <c r="A42" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>431</v>
+      <c r="B42" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F42" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="H42" s="20" t="s">
-        <v>442</v>
-      </c>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="L42" s="21"/>
+      <c r="G42" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="L42" s="20"/>
     </row>
     <row r="43" spans="1:12" ht="45" customHeight="1">
       <c r="A43" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>444</v>
+      <c r="B43" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E43" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F43" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F43" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="L43" s="21"/>
+      <c r="G43" s="18" t="s">
+        <v>544</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18" t="s">
+        <v>441</v>
+      </c>
+      <c r="L43" s="20"/>
     </row>
     <row r="44" spans="1:12" ht="45" customHeight="1">
       <c r="A44" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="B44" s="18" t="s">
-        <v>444</v>
+      <c r="B44" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F44" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F44" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="H44" s="20" t="s">
-        <v>449</v>
-      </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="L44" s="21"/>
+      <c r="G44" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="L44" s="20"/>
     </row>
     <row r="45" spans="1:12" ht="45" customHeight="1">
       <c r="A45" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="B45" s="18" t="s">
-        <v>444</v>
+      <c r="B45" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="E45" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F45" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F45" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="H45" s="20" t="s">
-        <v>452</v>
-      </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="L45" s="21"/>
+      <c r="G45" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="L45" s="20"/>
     </row>
     <row r="46" spans="1:12" ht="45" customHeight="1">
       <c r="A46" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="B46" s="18" t="s">
-        <v>444</v>
+      <c r="B46" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F46" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F46" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="H46" s="20" t="s">
-        <v>455</v>
-      </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="L46" s="21"/>
+      <c r="G46" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="L46" s="20"/>
     </row>
     <row r="47" spans="1:12" ht="45" customHeight="1">
       <c r="A47" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="B47" s="18" t="s">
-        <v>444</v>
+      <c r="B47" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F47" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F47" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="L47" s="21"/>
+      <c r="G47" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="L47" s="20"/>
     </row>
     <row r="48" spans="1:12" ht="45" customHeight="1">
       <c r="A48" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="B48" s="18" t="s">
-        <v>444</v>
+      <c r="B48" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F48" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F48" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="H48" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="L48" s="21"/>
+      <c r="G48" s="18" t="s">
+        <v>452</v>
+      </c>
+      <c r="H48" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="L48" s="20"/>
     </row>
     <row r="49" spans="1:12" ht="45" customHeight="1">
       <c r="A49" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B49" s="18" t="s">
-        <v>444</v>
+      <c r="B49" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="F49" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="F49" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>464</v>
-      </c>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="L49" s="21"/>
+      <c r="G49" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="L49" s="20"/>
     </row>
     <row r="50" spans="1:12" ht="36" customHeight="1">
       <c r="A50" s="12"/>
@@ -7665,19 +7656,19 @@
     </row>
     <row r="7" spans="1:12" ht="140.1" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>233</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>468</v>
+        <v>459</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>460</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="1"/>
@@ -7689,19 +7680,19 @@
     </row>
     <row r="8" spans="1:12" ht="140.1" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>470</v>
+        <v>461</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>462</v>
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="1"/>
@@ -7713,19 +7704,19 @@
     </row>
     <row r="9" spans="1:12" ht="140.1" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>235</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>472</v>
+        <v>463</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>464</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="1"/>
@@ -7737,19 +7728,19 @@
     </row>
     <row r="10" spans="1:12" ht="140.1" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>236</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>466</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>474</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="1"/>
@@ -7761,19 +7752,19 @@
     </row>
     <row r="11" spans="1:12" ht="140.1" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>237</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>476</v>
+        <v>467</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>468</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="1"/>
@@ -7785,19 +7776,19 @@
     </row>
     <row r="12" spans="1:12" ht="140.1" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>238</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>478</v>
+        <v>469</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>470</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="1"/>
@@ -7809,19 +7800,19 @@
     </row>
     <row r="13" spans="1:12" ht="140.1" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>239</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>480</v>
+        <v>471</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>472</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="1"/>
@@ -7833,19 +7824,19 @@
     </row>
     <row r="14" spans="1:12" ht="140.1" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>240</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>482</v>
+        <v>473</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>474</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="1"/>
@@ -7857,19 +7848,19 @@
     </row>
     <row r="15" spans="1:12" ht="140.1" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>241</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>484</v>
+        <v>475</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>476</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="1"/>
@@ -7881,19 +7872,19 @@
     </row>
     <row r="16" spans="1:12" ht="140.1" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>242</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>486</v>
+        <v>477</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>478</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="1"/>
@@ -7905,19 +7896,19 @@
     </row>
     <row r="17" spans="1:12" ht="140.1" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>243</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>488</v>
+        <v>479</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>480</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="1"/>
@@ -7929,19 +7920,19 @@
     </row>
     <row r="18" spans="1:12" ht="140.1" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>244</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>490</v>
+        <v>481</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>482</v>
       </c>
       <c r="F18" s="14"/>
       <c r="G18" s="1"/>
@@ -7953,19 +7944,19 @@
     </row>
     <row r="19" spans="1:12" ht="140.1" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>245</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>492</v>
+        <v>483</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>484</v>
       </c>
       <c r="F19" s="14"/>
       <c r="G19" s="1"/>
@@ -7977,19 +7968,19 @@
     </row>
     <row r="20" spans="1:12" ht="140.1" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>494</v>
+        <v>485</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>486</v>
       </c>
       <c r="F20" s="14"/>
       <c r="G20" s="1"/>
@@ -8001,19 +7992,19 @@
     </row>
     <row r="21" spans="1:12" ht="140.1" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>247</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>496</v>
+        <v>487</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>488</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -8025,19 +8016,19 @@
     </row>
     <row r="22" spans="1:12" ht="140.1" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>248</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>498</v>
+        <v>489</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>490</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -8049,19 +8040,19 @@
     </row>
     <row r="23" spans="1:12" ht="140.1" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>249</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>500</v>
+        <v>491</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>492</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -8073,19 +8064,19 @@
     </row>
     <row r="24" spans="1:12" ht="140.1" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>250</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>502</v>
+        <v>493</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>494</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -8097,19 +8088,19 @@
     </row>
     <row r="25" spans="1:12" ht="140.1" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>251</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>504</v>
+        <v>495</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>496</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -8121,19 +8112,19 @@
     </row>
     <row r="26" spans="1:12" ht="140.1" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>252</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>506</v>
+        <v>497</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>498</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -8145,19 +8136,19 @@
     </row>
     <row r="27" spans="1:12" ht="140.1" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>253</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>508</v>
+        <v>499</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>500</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -8169,19 +8160,19 @@
     </row>
     <row r="28" spans="1:12" ht="140.1" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>254</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>510</v>
+        <v>501</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>502</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -8193,19 +8184,19 @@
     </row>
     <row r="29" spans="1:12" ht="140.1" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>255</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>512</v>
+        <v>503</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>504</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -8217,19 +8208,19 @@
     </row>
     <row r="30" spans="1:12" ht="140.1" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>256</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>514</v>
+        <v>505</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>506</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -8241,19 +8232,19 @@
     </row>
     <row r="31" spans="1:12" ht="140.1" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>257</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>516</v>
+        <v>507</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>508</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -8265,19 +8256,19 @@
     </row>
     <row r="32" spans="1:12" ht="140.1" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>258</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>518</v>
+        <v>509</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>510</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -8289,19 +8280,19 @@
     </row>
     <row r="33" spans="1:12" ht="140.1" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>259</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>520</v>
+        <v>511</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>512</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -8313,19 +8304,19 @@
     </row>
     <row r="34" spans="1:12" ht="140.1" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>260</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>522</v>
+        <v>513</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>514</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -8337,19 +8328,19 @@
     </row>
     <row r="35" spans="1:12" ht="140.1" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>261</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>524</v>
+        <v>515</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>516</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -8361,19 +8352,19 @@
     </row>
     <row r="36" spans="1:12" ht="140.1" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>525</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>526</v>
+        <v>517</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>518</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -8385,19 +8376,19 @@
     </row>
     <row r="37" spans="1:12" ht="140.1" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>263</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>528</v>
+        <v>519</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>520</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -8409,19 +8400,19 @@
     </row>
     <row r="38" spans="1:12" ht="140.1" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>264</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>530</v>
+        <v>521</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>522</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -8433,19 +8424,19 @@
     </row>
     <row r="39" spans="1:12" ht="140.1" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>532</v>
+        <v>523</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>524</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -8457,19 +8448,19 @@
     </row>
     <row r="40" spans="1:12" ht="140.1" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>266</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>533</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>534</v>
+        <v>525</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>526</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -8481,19 +8472,19 @@
     </row>
     <row r="41" spans="1:12" ht="140.1" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>267</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>536</v>
+        <v>527</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>528</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -8505,19 +8496,19 @@
     </row>
     <row r="42" spans="1:12" ht="140.1" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>268</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>538</v>
+        <v>529</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>530</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -8529,19 +8520,19 @@
     </row>
     <row r="43" spans="1:12" ht="140.1" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>269</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>540</v>
+        <v>547</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>531</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -8553,19 +8544,19 @@
     </row>
     <row r="44" spans="1:12" ht="140.1" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>270</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>542</v>
+        <v>548</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>532</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -8577,19 +8568,19 @@
     </row>
     <row r="45" spans="1:12" ht="140.1" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>544</v>
+        <v>549</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>533</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -8601,19 +8592,19 @@
     </row>
     <row r="46" spans="1:12" ht="140.1" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>272</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>546</v>
+        <v>534</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>535</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -8625,19 +8616,19 @@
     </row>
     <row r="47" spans="1:12" ht="140.1" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>273</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>548</v>
+        <v>536</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>537</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -8649,19 +8640,19 @@
     </row>
     <row r="48" spans="1:12" ht="140.1" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>550</v>
+        <v>538</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>539</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -8673,19 +8664,19 @@
     </row>
     <row r="49" spans="1:12" ht="140.1" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>275</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>551</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>552</v>
+        <v>540</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>541</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
